--- a/Лаб3_Excel_вариант11.xlsx
+++ b/Лаб3_Excel_вариант11.xlsx
@@ -20,23 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t xml:space="preserve">Ведомость расчёта заработной платы отдела</t>
   </si>
   <si>
-    <t xml:space="preserve">Параметры расчёта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подоходный налог</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Надбавка от оклада</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стаж для надбавки, более (лет)</t>
-  </si>
-  <si>
     <t xml:space="preserve">№</t>
   </si>
   <si>
@@ -58,7 +46,7 @@
     <t xml:space="preserve">Начислено, руб.</t>
   </si>
   <si>
-    <t xml:space="preserve">Подоходный налог, руб.</t>
+    <t xml:space="preserve">Подоходный налог 13 %, руб.</t>
   </si>
   <si>
     <t xml:space="preserve">К выдаче, руб.</t>
@@ -124,32 +112,27 @@
     <t xml:space="preserve">ИТОГО</t>
   </si>
   <si>
-    <t xml:space="preserve">Пояснения</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Синим цветом выделены исходные данные (их можно менять, остальное пересчитается).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Надбавка = 10 % от оклада, если стаж больше 5 лет; иначе 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подоходный налог 13 % считается от суммы оклад + надбавка (допущение).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">К выдаче = оклад + надбавка − подоходный налог.</t>
+    <t xml:space="preserve">Условия расчёта:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подоходный налог — 13 % от начисленной суммы (оклад + надбавка).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Надбавка — 10 % от оклада, если стаж работы более 5 лет.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К выдаче = начислено − подоходный налог.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0%"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,20 +176,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="18"/>
       <color rgb="FF000000"/>
@@ -236,7 +205,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
@@ -282,28 +251,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -315,23 +268,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,11 +280,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,7 +322,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -461,7 +406,7 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:barChart>
-        <c:barDir val="bar"/>
+        <c:barDir val="col"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -469,7 +414,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Ведомость!I8</c:f>
+              <c:f>Ведомость!I3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -503,10 +448,10 @@
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="1"/>
+            <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
-            <c:showCatName val="1"/>
-            <c:showSerName val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
@@ -518,7 +463,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Ведомость!$B$9:$B$18</c:f>
+              <c:f>Ведомость!$B$4:$B$13</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
@@ -556,7 +501,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Ведомость!$I$9:$I$18</c:f>
+              <c:f>Ведомость!$I$4:$I$13</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="10"/>
@@ -596,16 +541,50 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="53196987"/>
-        <c:axId val="48182792"/>
+        <c:axId val="61360775"/>
+        <c:axId val="86078983"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="53196987"/>
+        <c:axId val="61360775"/>
         <c:scaling>
-          <c:orientation val="maxMin"/>
+          <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Сотрудники</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -632,7 +611,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48182792"/>
+        <c:crossAx val="86078983"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -640,7 +619,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48182792"/>
+        <c:axId val="86078983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -659,7 +638,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0"/>
+              <a:bodyPr rot="-5400000"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -716,7 +695,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53196987"/>
+        <c:crossAx val="61360775"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -750,14 +729,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>160560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>800640</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>140760</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>619560</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -765,8 +744,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="5191200"/>
-        <a:ext cx="7919640" cy="3599640"/>
+        <a:off x="0" y="4381560"/>
+        <a:ext cx="9359640" cy="3959640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -959,477 +938,443 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>95000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <f aca="false">IF(E4&gt;5,D4*0.1,0)</f>
+        <v>9500</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <f aca="false">D4+F4</f>
+        <v>104500</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <f aca="false">ROUND(G4*0.13,2)</f>
+        <v>13585</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <f aca="false">G4-H4</f>
+        <v>90915</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>78000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <f aca="false">IF(E5&gt;5,D5*0.1,0)</f>
+        <v>7800</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <f aca="false">D5+F5</f>
+        <v>85800</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <f aca="false">ROUND(G5*0.13,2)</f>
+        <v>11154</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <f aca="false">G5-H5</f>
+        <v>74646</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="4" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <f aca="false">IF(E6&gt;5,D6*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <f aca="false">D6+F6</f>
+        <v>65000</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <f aca="false">ROUND(G6*0.13,2)</f>
+        <v>8450</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <f aca="false">G6-H6</f>
+        <v>56550</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="5" t="n">
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <f aca="false">IF(E7&gt;5,D7*0.1,0)</f>
+        <v>5800</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <f aca="false">D7+F7</f>
+        <v>63800</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <f aca="false">ROUND(G7*0.13,2)</f>
+        <v>8294</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <f aca="false">G7-H7</f>
+        <v>55506</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="F8" s="5" t="n">
+        <f aca="false">IF(E8&gt;5,D8*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <f aca="false">D8+F8</f>
+        <v>62000</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <f aca="false">ROUND(G8*0.13,2)</f>
+        <v>8060</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <f aca="false">G8-H8</f>
+        <v>53940</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="B9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>55000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <f aca="false">IF(E9&gt;5,D9*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <f aca="false">D9+F9</f>
+        <v>55000</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <f aca="false">ROUND(G9*0.13,2)</f>
+        <v>7150</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <f aca="false">G9-H9</f>
+        <v>47850</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="B10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>70000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <f aca="false">IF(E10&gt;5,D10*0.1,0)</f>
+        <v>7000</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <f aca="false">D10+F10</f>
+        <v>77000</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <f aca="false">ROUND(G10*0.13,2)</f>
+        <v>10010</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <f aca="false">G10-H10</f>
+        <v>66990</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <f aca="false">IF(E11&gt;5,D11*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <f aca="false">D11+F11</f>
+        <v>42000</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <f aca="false">ROUND(G11*0.13,2)</f>
+        <v>5460</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <f aca="false">G11-H11</f>
+        <v>36540</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>67000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <f aca="false">IF(E12&gt;5,D12*0.1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <f aca="false">D12+F12</f>
+        <v>67000</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <f aca="false">ROUND(G12*0.13,2)</f>
+        <v>8710</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <f aca="false">G12-H12</f>
+        <v>58290</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>95000</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <f aca="false">IF(E9&gt;$D$6,D9*$D$5,0)</f>
-        <v>9500</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <f aca="false">D9+F9</f>
-        <v>104500</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <f aca="false">ROUND(G9*$D$4,2)</f>
-        <v>13585</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <f aca="false">G9-H9</f>
-        <v>90915</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>78000</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <f aca="false">IF(E10&gt;$D$6,D10*$D$5,0)</f>
-        <v>7800</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <f aca="false">D10+F10</f>
-        <v>85800</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <f aca="false">ROUND(G10*$D$4,2)</f>
-        <v>11154</v>
-      </c>
-      <c r="I10" s="11" t="n">
-        <f aca="false">G10-H10</f>
-        <v>74646</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>65000</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <f aca="false">IF(E11&gt;$D$6,D11*$D$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <f aca="false">D11+F11</f>
-        <v>65000</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <f aca="false">ROUND(G11*$D$4,2)</f>
-        <v>8450</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <f aca="false">G11-H11</f>
-        <v>56550</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>58000</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <f aca="false">IF(E12&gt;$D$6,D12*$D$5,0)</f>
-        <v>5800</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <f aca="false">D12+F12</f>
-        <v>63800</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <f aca="false">ROUND(G12*$D$4,2)</f>
-        <v>8294</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <f aca="false">G12-H12</f>
-        <v>55506</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>62000</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <f aca="false">IF(E13&gt;$D$6,D13*$D$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="n">
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <f aca="false">IF(E13&gt;5,D13*0.1,0)</f>
+        <v>6000</v>
+      </c>
+      <c r="G13" s="5" t="n">
         <f aca="false">D13+F13</f>
-        <v>62000</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <f aca="false">ROUND(G13*$D$4,2)</f>
-        <v>8060</v>
-      </c>
-      <c r="I13" s="11" t="n">
+        <v>66000</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <f aca="false">ROUND(G13*0.13,2)</f>
+        <v>8580</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <f aca="false">G13-H13</f>
-        <v>53940</v>
+        <v>57420</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <f aca="false">IF(E14&gt;$D$6,D14*$D$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="n">
-        <f aca="false">D14+F14</f>
-        <v>55000</v>
-      </c>
-      <c r="H14" s="11" t="n">
-        <f aca="false">ROUND(G14*$D$4,2)</f>
-        <v>7150</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <f aca="false">G14-H14</f>
-        <v>47850</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>70000</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <f aca="false">IF(E15&gt;$D$6,D15*$D$5,0)</f>
-        <v>7000</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <f aca="false">D15+F15</f>
-        <v>77000</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <f aca="false">ROUND(G15*$D$4,2)</f>
-        <v>10010</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <f aca="false">G15-H15</f>
-        <v>66990</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7" t="n">
+        <f aca="false">SUM(D4:D13)</f>
+        <v>652000</v>
+      </c>
+      <c r="E14" s="6"/>
+      <c r="F14" s="7" t="n">
+        <f aca="false">SUM(F4:F13)</f>
+        <v>36100</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <f aca="false">SUM(G4:G13)</f>
+        <v>688100</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <f aca="false">SUM(H4:H13)</f>
+        <v>89453</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <f aca="false">SUM(I4:I13)</f>
+        <v>598647</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>42000</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <f aca="false">IF(E16&gt;$D$6,D16*$D$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <f aca="false">D16+F16</f>
-        <v>42000</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <f aca="false">ROUND(G16*$D$4,2)</f>
-        <v>5460</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <f aca="false">G16-H16</f>
-        <v>36540</v>
+      <c r="A16" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>67000</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <f aca="false">IF(E17&gt;$D$6,D17*$D$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <f aca="false">D17+F17</f>
-        <v>67000</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <f aca="false">ROUND(G17*$D$4,2)</f>
-        <v>8710</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <f aca="false">G17-H17</f>
-        <v>58290</v>
+      <c r="A17" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <f aca="false">IF(E18&gt;$D$6,D18*$D$5,0)</f>
-        <v>6000</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <f aca="false">D18+F18</f>
-        <v>66000</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <f aca="false">ROUND(G18*$D$4,2)</f>
-        <v>8580</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <f aca="false">G18-H18</f>
-        <v>57420</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13" t="s">
+      <c r="A19" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="14" t="n">
-        <f aca="false">SUM(D9:D18)</f>
-        <v>652000</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="14" t="n">
-        <f aca="false">SUM(F9:F18)</f>
-        <v>36100</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <f aca="false">SUM(G9:G18)</f>
-        <v>688100</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <f aca="false">SUM(H9:H18)</f>
-        <v>89453</v>
-      </c>
-      <c r="I19" s="14" t="n">
-        <f aca="false">SUM(I9:I18)</f>
-        <v>598647</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
-        <v>38</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
